--- a/Config/Datas/Tables/g_关卡_StageConfig.xlsx
+++ b/Config/Datas/Tables/g_关卡_StageConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbStage" sheetId="1" r:id="Rc6cdfc9f377c4341"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbStage" sheetId="1" r:id="Rbacf4dd89cf14ce5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -62,8 +62,68 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -95,8 +155,28 @@
         <x:fgColor rgb="FF64748B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F8FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -158,11 +238,25 @@
         <x:color rgb="FFCBD5E1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="76">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -256,6 +350,131 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -458,65 +677,155 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="25" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="58" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
+      <x:c r="B1" s="58" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="str">
+      <x:c r="C1" s="58" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="D1" s="11" t="str">
+      <x:c r="D1" s="58" t="str">
         <x:v>mapId</x:v>
       </x:c>
+      <x:c r="E1" s="58" t="str">
+        <x:v>stageRuleId</x:v>
+      </x:c>
+      <x:c r="F1" s="58" t="str">
+        <x:v>combatRulesId</x:v>
+      </x:c>
+      <x:c r="G1" s="58" t="str">
+        <x:v>presentationId</x:v>
+      </x:c>
+      <x:c r="H1" s="58" t="str">
+        <x:v>uiSetId</x:v>
+      </x:c>
+      <x:c r="I1" s="58" t="str">
+        <x:v>initialCharacterId</x:v>
+      </x:c>
+      <x:c r="J1" s="58" t="str">
+        <x:v>initialSkillIds</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="29" t="str">
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="61" t="str">
         <x:v>##type</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="str">
+      <x:c r="B2" s="61" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="str">
+      <x:c r="C2" s="61" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str">
+      <x:c r="D2" s="61" t="str">
         <x:v>int#ref=TbMap</x:v>
       </x:c>
+      <x:c r="E2" s="61" t="str">
+        <x:v>int#ref=TbStageRule</x:v>
+      </x:c>
+      <x:c r="F2" s="61" t="str">
+        <x:v>int#ref=TbCombatRules</x:v>
+      </x:c>
+      <x:c r="G2" s="61" t="str">
+        <x:v>int#ref=TbCombatPresentation</x:v>
+      </x:c>
+      <x:c r="H2" s="61" t="str">
+        <x:v>int?#ref=TbCombatUiSet</x:v>
+      </x:c>
+      <x:c r="I2" s="61" t="str">
+        <x:v>int#ref=TbCharacter</x:v>
+      </x:c>
+      <x:c r="J2" s="61" t="str">
+        <x:v>(list#sep=;),int#ref=TbSkill</x:v>
+      </x:c>
     </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="30" t="str">
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="65" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B3" s="16"/>
-      <x:c r="C3" s="16"/>
-      <x:c r="D3" s="16"/>
+      <x:c r="B3" s="66"/>
+      <x:c r="C3" s="66"/>
+      <x:c r="D3" s="66"/>
+      <x:c r="E3" s="66"/>
+      <x:c r="F3" s="66"/>
+      <x:c r="G3" s="66"/>
+      <x:c r="H3" s="66"/>
+      <x:c r="I3" s="66"/>
+      <x:c r="J3" s="66"/>
     </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="31" t="str">
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="69" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B4" s="23" t="str">
+      <x:c r="B4" s="70" t="str">
         <x:v>关卡ID</x:v>
       </x:c>
-      <x:c r="C4" s="23" t="str">
+      <x:c r="C4" s="70" t="str">
         <x:v>关卡名称</x:v>
       </x:c>
-      <x:c r="D4" s="24" t="str">
-        <x:v>地图ID；本轮仅预留表结构</x:v>
+      <x:c r="D4" s="70" t="str">
+        <x:v>地图ID</x:v>
+      </x:c>
+      <x:c r="E4" s="70" t="str">
+        <x:v>单局规则ID</x:v>
+      </x:c>
+      <x:c r="F4" s="70" t="str">
+        <x:v>战斗规则ID</x:v>
+      </x:c>
+      <x:c r="G4" s="70" t="str">
+        <x:v>战斗表现方案ID</x:v>
+      </x:c>
+      <x:c r="H4" s="70" t="str">
+        <x:v>正式UI方案；Prefab完成后填写</x:v>
+      </x:c>
+      <x:c r="I4" s="70" t="str">
+        <x:v>初始角色ID</x:v>
+      </x:c>
+      <x:c r="J4" s="70" t="str">
+        <x:v>初始技能列表</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" s="32"/>
-      <x:c r="D5" s="32"/>
+      <x:c r="A5" s="50"/>
+      <x:c r="B5" s="75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="50" t="str">
+        <x:v>测试关卡</x:v>
+      </x:c>
+      <x:c r="D5" s="75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="50"/>
+      <x:c r="I5" s="50" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="J5" s="50" t="str">
+        <x:v>20001</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/g_关卡_StageConfig.xlsx
+++ b/Config/Datas/Tables/g_关卡_StageConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbStage" sheetId="1" r:id="Rbacf4dd89cf14ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbStage" sheetId="1" r:id="R2de36e5ef17a4e9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -790,7 +790,7 @@
         <x:v>战斗表现方案ID</x:v>
       </x:c>
       <x:c r="H4" s="70" t="str">
-        <x:v>正式UI方案；Prefab完成后填写</x:v>
+        <x:v>正式UI方案ID</x:v>
       </x:c>
       <x:c r="I4" s="70" t="str">
         <x:v>初始角色ID</x:v>
@@ -819,7 +819,9 @@
       <x:c r="G5" s="50" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H5" s="50"/>
+      <x:c r="H5" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="I5" s="50" t="n">
         <x:v>10001</x:v>
       </x:c>
